--- a/content/automated-testing/data/dance-schedule.xlsx
+++ b/content/automated-testing/data/dance-schedule.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="181">
   <si>
     <t>Time</t>
   </si>
@@ -149,10 +149,6 @@
 GCA: John Ryan</t>
   </si>
   <si>
-    <t xml:space="preserve">C3A : Dancing - Vic Ceder
-GCA: Jenn Engimann</t>
-  </si>
-  <si>
     <t xml:space="preserve">C1 : Dancing - Barry Clasper
 GCA: Jane Clewe</t>
   </si>
@@ -547,9 +543,6 @@
   </si>
   <si>
     <t>C1 : Dancing - Dayle Hodge</t>
-  </si>
-  <si>
-    <t>C2 : Dancing - Dayle Hodge</t>
   </si>
   <si>
     <t>3:00p-4:00p</t>
@@ -1206,106 +1199,106 @@
         <v>36</v>
       </c>
       <c r="I5" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J5" s="4" t="s">
         <v>37</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="6" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="C6" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="D6" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="F6" s="4" t="s">
         <v>43</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>44</v>
       </c>
       <c r="G6" s="4"/>
       <c r="H6" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="I6" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="J6" s="4" t="s">
         <v>46</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="7" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="C7" s="4" t="s">
         <v>49</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>50</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F7" s="4" t="s">
         <v>51</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>52</v>
       </c>
       <c r="G7" s="4"/>
       <c r="H7" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I7" s="4"/>
       <c r="J7" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="C8" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="D8" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="E8" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="F8" s="4" t="s">
         <v>59</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>60</v>
       </c>
       <c r="G8" s="4"/>
       <c r="H8" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I8" s="4"/>
       <c r="J8" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
       <c r="F9" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
@@ -1360,13 +1353,13 @@
     </row>
     <row r="2" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="C2" s="4" t="s">
         <v>66</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>67</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
@@ -1377,27 +1370,27 @@
     </row>
     <row r="3" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="H3" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="I3" s="4" t="s">
         <v>73</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="4" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1405,26 +1398,26 @@
         <v>16</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="D4" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="4" t="s">
         <v>77</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>78</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="H4" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="I4" s="4" t="s">
         <v>80</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="5" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1432,24 +1425,24 @@
         <v>24</v>
       </c>
       <c r="B5" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>82</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>83</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F5" s="4"/>
       <c r="G5" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="H5" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="I5" s="4" t="s">
         <v>86</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="6" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1457,113 +1450,113 @@
         <v>31</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="D6" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>90</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>91</v>
       </c>
       <c r="F6" s="4"/>
       <c r="G6" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="H6" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="I6" s="4" t="s">
         <v>93</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="7" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B7" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="D7" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="E7" s="4" t="s">
         <v>97</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>98</v>
       </c>
       <c r="F7" s="4"/>
       <c r="G7" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="H7" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="I7" s="4" t="s">
         <v>100</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="8" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B8" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>102</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>103</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F8" s="4"/>
       <c r="G8" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="H8" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="I8" s="4" t="s">
         <v>106</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="9" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B9" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>108</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>109</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F9" s="4"/>
       <c r="G9" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="H9" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="I9" s="4" t="s">
         <v>112</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="10" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
       <c r="D10" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
@@ -1573,10 +1566,10 @@
     </row>
     <row r="11" ht="48" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>115</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -1630,264 +1623,264 @@
     </row>
     <row r="2" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="C2" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>120</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>121</v>
       </c>
       <c r="F2" s="4"/>
       <c r="G2" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="H2" s="4" t="s">
         <v>122</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>123</v>
       </c>
       <c r="I2" s="4"/>
       <c r="J2" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="C3" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="E3" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="F3" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="H3" s="4" t="s">
         <v>131</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>132</v>
       </c>
       <c r="I3" s="4"/>
       <c r="J3" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="4" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="D4" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="4" t="s">
         <v>136</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>137</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="H4" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="I4" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="J4" s="4" t="s">
         <v>140</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="5" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
       <c r="E5" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>143</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>144</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>21</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="J5" s="4"/>
     </row>
     <row r="6" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
       <c r="E6" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="G6" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="H6" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="I6" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="J6" s="4" t="s">
         <v>151</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="7" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
       <c r="E7" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="G7" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="H7" s="4" t="s">
         <v>156</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>158</v>
       </c>
       <c r="I7" s="4"/>
       <c r="J7" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="8" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="G8" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="H8" s="4" t="s">
         <v>162</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>164</v>
       </c>
       <c r="I8" s="4"/>
       <c r="J8" s="4" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="9" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
       <c r="F9" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="H9" s="4" t="s">
         <v>167</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>169</v>
       </c>
       <c r="I9" s="4"/>
       <c r="J9" s="4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="10" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="G10" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="H10" s="4" t="s">
         <v>173</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>175</v>
       </c>
       <c r="I10" s="4"/>
       <c r="J10" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
       <c r="F11" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="H11" s="4" t="s">
         <v>178</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>180</v>
       </c>
       <c r="I11" s="4"/>
       <c r="J11" s="4" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="12" ht="48" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>
